--- a/anexo/projetoPI.xlsx
+++ b/anexo/projetoPI.xlsx
@@ -1,324 +1,189 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11850"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="11850" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
-  <si>
-    <t>Turmas</t>
-  </si>
-  <si>
-    <t>Responsável</t>
-  </si>
-  <si>
-    <t>Secretaria/Autarquia</t>
-  </si>
-  <si>
-    <t>E-mail</t>
-  </si>
-  <si>
-    <t>Endereço</t>
-  </si>
-  <si>
-    <t>Participantes</t>
-  </si>
-  <si>
-    <t>Autorização</t>
-  </si>
-  <si>
-    <t>Lista de presença</t>
-  </si>
-  <si>
-    <t>Publicações - Instagram</t>
-  </si>
-  <si>
-    <t>Publicações - Facebook</t>
-  </si>
-  <si>
-    <t>Publicações - Outras</t>
-  </si>
-  <si>
-    <t>Ano</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>numero participantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formalizacao </t>
-  </si>
-  <si>
-    <t>imagem</t>
-  </si>
-  <si>
-    <t>indicado dat@</t>
-  </si>
-  <si>
-    <t>nome da escola</t>
-  </si>
-  <si>
-    <t>conte</t>
-  </si>
-  <si>
-    <t>visita</t>
-  </si>
-  <si>
-    <t>Tempo dedicado</t>
-  </si>
-  <si>
-    <t>Manhã</t>
-  </si>
-  <si>
-    <t>lucimara</t>
-  </si>
-  <si>
-    <t>iria</t>
-  </si>
-  <si>
-    <t>luiz@email</t>
-  </si>
-  <si>
-    <t>av rui</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>link 1</t>
-  </si>
-  <si>
-    <t>link 2</t>
-  </si>
-  <si>
-    <t>link 3</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>agendado</t>
-  </si>
-  <si>
-    <t>13/05/2026</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>fotos\pngtree-flat-style-money-icon-on-orange-background-perfect-for-web-design-png-image_12325323.png</t>
-  </si>
-  <si>
-    <t>Ótimo</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -619,154 +484,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -820,11 +684,74 @@
     <cellStyle name="60% - Ênfase 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1084,170 +1011,405 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:V2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="25.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="29.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="14.8571428571429" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="14.5714285714286" customWidth="1"/>
-    <col min="11" max="11" width="15.1428571428571" customWidth="1"/>
-    <col min="12" max="12" width="11.2857142857143" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="20.7142857142857" customWidth="1"/>
-    <col min="16" max="16" width="18.5714285714286" customWidth="1"/>
-    <col min="17" max="17" width="13.5714285714286" customWidth="1"/>
-    <col min="18" max="18" width="19.4285714285714" customWidth="1"/>
-    <col min="19" max="19" width="15.2857142857143" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="22" max="22" width="17.5714285714286" customWidth="1"/>
+    <col width="14.7142857142857" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25.4285714285714" customWidth="1" min="4" max="4"/>
+    <col width="29.5714285714286" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Turmas</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Secretaria/autarquia</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Endereço</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Participantes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Autorização</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Lista de presença</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Publicações - Instagram</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Publicações - Facebook</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Publicações - Outras</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>conte</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>visita</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Tempo dedicado</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:22">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" t="s">
-        <v>38</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>lucimara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>secretaria municipal padre julio</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>luiz@gmail.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>rua antonio freitas</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>lucimara</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">link insta </t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>link face</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>link outro</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>agendado</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>form da acao</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>fotos\tela-app.JPG</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ind-data</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>E. E. TANQCREDO NEVES</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Ótimo</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Bom</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lucimara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>autorquia geral</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>lucas#@gamil</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AV jjsh</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>hffg</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>hghj</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>gfhdf</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>confirm</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ghff</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>gfhdf</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lucimara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>autorquia geral</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>lucas#@gamil</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AV jjsh</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>hffg</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>hghj</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>gfhdf</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>confirm</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ghff</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>gfhdf</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Ótimo</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ótimo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ótimo</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>